--- a/Bioinformatics/Samples_RNAsep2.xlsx
+++ b/Bioinformatics/Samples_RNAsep2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tsoldo01/Documents/Recherche/rnasep/Bioinformatics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tsoldo01/Documents/Recherche/Current/rnasep/Bioinformatics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E361E646-7507-2947-9199-DD2C41A47D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2E82B3-9A1F-F94C-8B3F-306BD11DCDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18320" yWindow="-22140" windowWidth="23240" windowHeight="15940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -586,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -601,7 +601,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1349,10 +1348,9 @@
       <c r="F2" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="14"/>
       <c r="I2" s="12" t="s">
         <v>99</v>
       </c>
@@ -1376,10 +1374,9 @@
       <c r="F3" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="10" t="s">
